--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.77" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.77" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.77.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.77.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0077.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0077.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -819,7 +819,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.77.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.77" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.77" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -422,18 +422,18 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="51" customWidth="1" min="14" max="14"/>
-    <col width="35" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -595,28 +595,32 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr"/>
       <c r="I2" s="1" t="inlineStr"/>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the Order:â€”</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Masterâ€™s refu-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]70</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]70</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 70</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr"/>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]70</t>
+        </is>
+      </c>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L52: punctuation artifact: repeated periods :: down the cause. Â°..</t>
+          <t>L52: punctuation artifact: repeated periods :: down the cause. °..</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -650,16 +654,8 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L163: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the Order:â€”</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Defendant, to 1â€”</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
+      <c r="K3" s="1" t="inlineStr"/>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
@@ -701,16 +697,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L173: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œIf the Pl:</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L68: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The following is the Order :â€”</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -738,12 +726,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -945,12 +933,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -989,7 +977,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1028,7 +1016,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
